--- a/回後買上漲圖表(基礎版)_20260615/回後買上漲基礎版_20260615.xlsx
+++ b/回後買上漲圖表(基礎版)_20260615/回後買上漲基礎版_20260615.xlsx
@@ -487,11 +487,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -551,31 +551,31 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3311.TW</t>
+          <t>8932.TWO</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>閎暉</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>41.3</v>
+        <v>106.5</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>38.15</v>
+        <v>102</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>3901</v>
+        <v>11173</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1702</v>
+        <v>4880</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>2.3</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>36.54</v>
+        <v>100.97</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -586,31 +586,31 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>3041.TW</t>
+          <t>2439.TW</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>揚智</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>27</v>
+        <v>92.3</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>25.55</v>
+        <v>90</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>5627</v>
+        <v>5573</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>2588</v>
+        <v>2584</v>
       </c>
       <c r="G3" s="10" t="n">
         <v>2.2</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>25.15</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -621,31 +621,31 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>5392.TWO</t>
+          <t>3576.TW</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>聯合再生</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>44.9</v>
+        <v>19.8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>43.8</v>
+        <v>18.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>6957</v>
+        <v>74101</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3295</v>
+        <v>38540</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>43.81</v>
+        <v>18.17</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -656,31 +656,31 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>4952.TW</t>
+          <t>2905.TW</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>凌通</t>
+          <t>三商</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>58.5</v>
+        <v>14.9</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>56.6</v>
+        <v>14.5</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>4834</v>
+        <v>1859</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>2361</v>
+        <v>1027</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>51.86</v>
+        <v>13.86</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2010.TW</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>春源</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>202</v>
+        <v>24.6</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>191</v>
+        <v>24.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13702</v>
+        <v>2756</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7004</v>
+        <v>1668</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>197.45</v>
+        <v>23.33</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -726,31 +726,31 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>8215.TW</t>
+          <t>2413.TW</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>環科</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>30.55</v>
+        <v>61.2</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>29.85</v>
+        <v>61</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>8979</v>
+        <v>23193</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>4618</v>
+        <v>14765</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>29.35</v>
+        <v>52.79</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -761,31 +761,31 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>6220.TWO</t>
+          <t>3152.TWO</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>璟德</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>37</v>
+        <v>221</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>35.45</v>
+        <v>208</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2683</v>
+        <v>4213</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1405</v>
+        <v>2597</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>33.08</v>
+        <v>188.02</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -796,31 +796,31 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2375.TW</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>凱美</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>189.5</v>
+        <v>20.4</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>177</v>
+        <v>19.65</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>13541</v>
+        <v>79066</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>7981</v>
+        <v>51528</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>149.82</v>
+        <v>19.13</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -831,31 +831,31 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>6668.TW</t>
+          <t>2034.TW</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>允強</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>39.85</v>
+        <v>20.25</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>39.05</v>
+        <v>20.15</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1742</v>
+        <v>2586</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1026</v>
+        <v>1782</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>39</v>
+        <v>20.1</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -866,31 +866,31 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>3321.TW</t>
+          <t>6196.TW</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>同泰</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>22.45</v>
+        <v>548</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>20.95</v>
+        <v>521</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>1826</v>
+        <v>3889</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>1155</v>
+        <v>2591</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>18.94</v>
+        <v>484.88</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>3717.TW</t>
+          <t>2634.TW</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>聯嘉投控</t>
+          <t>漢翔</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>22.25</v>
+        <v>47.15</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>20.65</v>
+        <v>46.95</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3470</v>
+        <v>5663</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2130</v>
+        <v>4045</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>22.14</v>
+        <v>46.37</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -936,31 +936,31 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>3294.TWO</t>
+          <t>2903.TW</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>英濟</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>39.4</v>
+        <v>23.85</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>36.8</v>
+        <v>23.35</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2387</v>
+        <v>4753</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>1457</v>
+        <v>3366</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>39.35</v>
+        <v>22.5</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -971,31 +971,31 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>1307.TW</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>590</v>
+        <v>36.75</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>578</v>
+        <v>35.6</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>50819</v>
+        <v>2834</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>33280</v>
+        <v>2095</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>509.6</v>
+        <v>32.84</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1006,31 +1006,31 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>4721.TWO</t>
+          <t>8105.TW</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>美琪瑪</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>101</v>
+        <v>22.45</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>95.59999999999999</v>
+        <v>21.45</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>4665</v>
+        <v>41248</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3422</v>
+        <v>28998</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>1.4</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>90.42</v>
+        <v>18.61</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1041,31 +1041,31 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>8936.TWO</t>
+          <t>2536.TW</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>國統</t>
+          <t>宏普</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>57.9</v>
+        <v>21.95</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>57.7</v>
+        <v>21.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>14159</v>
+        <v>1466</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>9859</v>
+        <v>1027</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>1.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>53.81</v>
+        <v>20.23</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -1076,31 +1076,31 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>6719.TW</t>
+          <t>2302.TW</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>麗正</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>240.5</v>
+        <v>34.65</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>224.5</v>
+        <v>31.5</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>1480</v>
+        <v>1715</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>1103</v>
+        <v>1245</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>235.82</v>
+        <v>32.19</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1111,31 +1111,31 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>3019.TW</t>
+          <t>2204.TW</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>亞光</t>
+          <t>中華</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>158</v>
+        <v>56.6</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>151.5</v>
+        <v>55.9</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>16716</v>
+        <v>1855</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>13014</v>
+        <v>1297</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>151.18</v>
+        <v>54.04</v>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
@@ -1146,31 +1146,31 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>3707.TWO</t>
+          <t>3665.TW</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>漢磊</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>81.7</v>
+        <v>2310</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>79.90000000000001</v>
+        <v>2280</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>14868</v>
+        <v>3902</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>11103</v>
+        <v>3057</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>1.3</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>79.87</v>
+        <v>2158.75</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1181,31 +1181,31 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>3260.TWO</t>
+          <t>2887.TW</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>423</v>
+        <v>30.2</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>422</v>
+        <v>28.9</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>16518</v>
+        <v>157208</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>12895</v>
+        <v>116897</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>1.3</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>417.52</v>
+        <v>25.82</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
@@ -1216,31 +1216,31 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>6187.TWO</t>
+          <t>1808.TW</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>潤隆</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>1130</v>
+        <v>31.9</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>1110</v>
+        <v>31.7</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>3124</v>
+        <v>3072</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2531</v>
+        <v>2322</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>1109.25</v>
+        <v>29.91</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1251,31 +1251,31 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2465.TW</t>
+          <t>3322.TWO</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>麗臺</t>
+          <t>建舜電</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>83</v>
+        <v>15.35</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>15.2</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2315</v>
+        <v>2628</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1902</v>
+        <v>2284</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>1.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>82.28</v>
+        <v>13.71</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -1286,31 +1286,31 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>3596.TW</t>
+          <t>2014.TW</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>中鴻</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>190.5</v>
+        <v>18</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>186.5</v>
+        <v>17.65</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1922</v>
+        <v>8916</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1613</v>
+        <v>7315</v>
       </c>
       <c r="G23" s="10" t="n">
         <v>1.2</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>186.65</v>
+        <v>17.9</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
@@ -1321,31 +1321,31 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>6259.TWO</t>
+          <t>7780.TW</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>30.35</v>
+        <v>18.8</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>29.65</v>
+        <v>18.55</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2909</v>
+        <v>3013</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2340</v>
+        <v>2511</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>1.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>26.54</v>
+        <v>18.11</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
@@ -1356,31 +1356,31 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>9933.TW</t>
+          <t>1608.TW</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>中鼎</t>
+          <t>華榮</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>42.8</v>
+        <v>34.4</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>42.1</v>
+        <v>33.7</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>8074</v>
+        <v>5673</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>6982</v>
+        <v>4877</v>
       </c>
       <c r="G25" s="10" t="n">
         <v>1.2</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>40.42</v>
+        <v>34.21</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1391,31 +1391,31 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1563.TW</t>
+          <t>9945.TW</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>64</v>
+        <v>26.8</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>61.7</v>
+        <v>26.2</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1147</v>
+        <v>14890</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1080</v>
+        <v>14123</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>1.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>58.29</v>
+        <v>24.27</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1426,31 +1426,31 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>3234.TWO</t>
+          <t>6139.TW</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>光環</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>122.5</v>
+        <v>805</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>116</v>
+        <v>767</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2834</v>
+        <v>5499</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>2611</v>
+        <v>5000</v>
       </c>
       <c r="G27" s="10" t="n">
         <v>1.1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>113.82</v>
+        <v>771.95</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -1461,31 +1461,31 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>6770.TW</t>
+          <t>5469.TW</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>瀚宇博</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>73.3</v>
+        <v>83.7</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>68</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>86191</v>
+        <v>3015</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>81471</v>
+        <v>2852</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>1.1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>72.16</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1496,31 +1496,31 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2337.TW</t>
+          <t>3060.TW</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>銘異</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>159</v>
+        <v>31.15</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>148</v>
+        <v>29.95</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>27698</v>
+        <v>2824</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>24157</v>
+        <v>2532</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>1.1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>152.57</v>
+        <v>29.49</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1531,31 +1531,31 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2316.TW</t>
+          <t>2206.TW</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>楠梓電</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>171.5</v>
+        <v>63</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>162</v>
+        <v>61.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5669</v>
+        <v>1993</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5109</v>
+        <v>1893</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>1.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>160.98</v>
+        <v>60.8</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1566,31 +1566,31 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>3008.TW</t>
+          <t>2393.TW</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>億光</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>4420</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>4355</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>3671</v>
+        <v>5528</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>3693</v>
+        <v>4935</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>3742.5</v>
+        <v>65.2</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1601,31 +1601,31 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>3504.TW</t>
+          <t>2615.TW</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2329</v>
+        <v>12769</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2384</v>
+        <v>11659</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>79.64</v>
+        <v>82.83</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1636,31 +1636,31 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>5536.TWO</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>61.6</v>
+        <v>1180</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>60.25</v>
+        <v>1125</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>31476</v>
+        <v>1105</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>30888</v>
+        <v>1150</v>
       </c>
       <c r="G33" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>59.59</v>
+        <v>1031.55</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1671,31 +1671,31 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>8110.TW</t>
+          <t>6214.TW</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>57.5</v>
+        <v>145.5</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>57</v>
+        <v>144.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>11322</v>
+        <v>2251</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>11809</v>
+        <v>2349</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>55.48</v>
+        <v>137</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1706,31 +1706,31 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>6166.TW</t>
+          <t>4532.TW</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>瑞智</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>141</v>
+        <v>24.45</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>134.5</v>
+        <v>24.25</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>3680</v>
+        <v>1074</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>3791</v>
+        <v>1055</v>
       </c>
       <c r="G35" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>128.6</v>
+        <v>23.98</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -1741,31 +1741,31 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>4973.TWO</t>
+          <t>2646.TW</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>廣穎</t>
+          <t>星宇航空</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>210</v>
+        <v>20.6</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>199</v>
+        <v>20.3</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>3151</v>
+        <v>5954</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3130</v>
+        <v>5895</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>154.6</v>
+        <v>20.37</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -1776,31 +1776,31 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>3049.TW</t>
+          <t>2851.TW</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>精金</t>
+          <t>中再保</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>14.75</v>
+        <v>37.15</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>14.5</v>
+        <v>37</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>11301</v>
+        <v>1902</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>11470</v>
+        <v>1988</v>
       </c>
       <c r="G37" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>13.65</v>
+        <v>35.69</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -1811,31 +1811,31 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>6788.TWO</t>
+          <t>5351.TWO</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>449</v>
+        <v>88.7</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>428</v>
+        <v>88.5</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2077</v>
+        <v>27894</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2174</v>
+        <v>28198</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>414.28</v>
+        <v>84.28</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -1846,31 +1846,31 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>4760.TWO</t>
+          <t>1434.TW</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>401.5</v>
+        <v>16.65</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>389</v>
+        <v>16.6</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>1606</v>
+        <v>2237</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>1764</v>
+        <v>2329</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>383.18</v>
+        <v>15.74</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -1881,31 +1881,31 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>1313.TW</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>141.5</v>
+        <v>11.25</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>137.5</v>
+        <v>11.2</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>328524</v>
+        <v>4214</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>353297</v>
+        <v>4185</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>128.9</v>
+        <v>10.86</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -1916,31 +1916,31 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>2352.TW</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>佳世達</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>2375</v>
+        <v>31</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>2325</v>
+        <v>30.35</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>27846</v>
+        <v>8353</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>32011</v>
+        <v>9485</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>0.9</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>2300.04</v>
+        <v>29.35</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -1951,31 +1951,31 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>2641.TWO</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>正德</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>624</v>
+        <v>18.8</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>584</v>
+        <v>18.7</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1908</v>
+        <v>2913</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2151</v>
+        <v>3177</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>0.9</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>563.4</v>
+        <v>18.47</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -1986,31 +1986,31 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>6269.TW</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>4470</v>
+        <v>72.3</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>4415</v>
+        <v>70.5</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>11647</v>
+        <v>8094</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>12697</v>
+        <v>9023</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>0.9</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>4172.75</v>
+        <v>65.42</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2021,31 +2021,31 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>3704.TW</t>
+          <t>6153.TW</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>嘉聯益</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>47.7</v>
+        <v>22.25</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>47.4</v>
+        <v>21.1</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>4367</v>
+        <v>28567</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5088</v>
+        <v>30291</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>0.9</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>45.34</v>
+        <v>18.99</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2056,31 +2056,31 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>3044.TW</t>
+          <t>1708.TW</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>東鹼</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>520</v>
+        <v>48</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>509</v>
+        <v>46.85</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>3476</v>
+        <v>11596</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>3939</v>
+        <v>12297</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>0.9</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>497.5</v>
+        <v>41.2</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2091,31 +2091,31 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>6548.TWO</t>
+          <t>1326.TW</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>91.8</v>
+        <v>48.8</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>89.7</v>
+        <v>47.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2846</v>
+        <v>21643</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3519</v>
+        <v>23253</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>72.95</v>
+        <v>48.34</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2126,31 +2126,31 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>0055.TW</t>
+          <t>2002.TW</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>元大MSCI金融</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>41</v>
+        <v>18.9</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>40.57</v>
+        <v>18.7</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>967</v>
+        <v>57479</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1190</v>
+        <v>64652</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>36.82</v>
+        <v>18.85</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2161,31 +2161,31 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>5426.TWO</t>
+          <t>6585.TW</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>振發</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>35.6</v>
+        <v>136</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>32.8</v>
+        <v>130</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>3009</v>
+        <v>1892</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3891</v>
+        <v>2291</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>24.7</v>
+        <v>105.38</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2196,31 +2196,31 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>3093.TWO</t>
+          <t>5864.TWO</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>港建*</t>
+          <t>致和證</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>64.7</v>
+        <v>47.2</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>62.4</v>
+        <v>43.95</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>3458</v>
+        <v>8930</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>4546</v>
+        <v>11095</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>56.53</v>
+        <v>41.04</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2231,31 +2231,31 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>1609.TW</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>大亞</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1920</v>
+        <v>37.3</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1830</v>
+        <v>36.7</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>3767</v>
+        <v>5918</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4604</v>
+        <v>7587</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>1789.25</v>
+        <v>37.13</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2266,31 +2266,31 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2405.TW</t>
+          <t>1342.TW</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>輔信</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>19.45</v>
+        <v>117.5</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>19.25</v>
+        <v>111</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>4285</v>
+        <v>2096</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>5586</v>
+        <v>2554</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>18.12</v>
+        <v>98.42</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2301,31 +2301,31 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2428.TW</t>
+          <t>1709.TW</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>興勤</t>
+          <t>和益</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>310</v>
+        <v>21.35</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>302</v>
+        <v>21.15</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>3339</v>
+        <v>1697</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4078</v>
+        <v>2205</v>
       </c>
       <c r="G52" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>268.35</v>
+        <v>19.59</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2336,31 +2336,31 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>5009.TWO</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>榮剛</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>960</v>
+        <v>36.3</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>930</v>
+        <v>35.55</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>16532</v>
+        <v>2692</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>20831</v>
+        <v>3202</v>
       </c>
       <c r="G53" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>958</v>
+        <v>35.94</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2371,31 +2371,31 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2329.TW</t>
+          <t>2323.TW</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>中環</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>55.7</v>
+        <v>11.2</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>55.3</v>
+        <v>11.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>6442</v>
+        <v>9946</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>8000</v>
+        <v>12938</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>55.11</v>
+        <v>10.71</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2406,31 +2406,31 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>4976.TW</t>
+          <t>9904.TW</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>佳凌</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>34.6</v>
+        <v>26.65</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>34.05</v>
+        <v>26.45</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>2917</v>
+        <v>17817</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>3887</v>
+        <v>21723</v>
       </c>
       <c r="G55" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>32.71</v>
+        <v>26</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2441,31 +2441,31 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>3114.TWO</t>
+          <t>9940.TW</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>好德</t>
+          <t>信義</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>43.45</v>
+        <v>19.75</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>41.95</v>
+        <v>19.55</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>960</v>
+        <v>986</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1212</v>
+        <v>1204</v>
       </c>
       <c r="G56" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>34.79</v>
+        <v>18.54</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2476,31 +2476,31 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>4534.TWO</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>慶騰</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>51.4</v>
+        <v>33</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>50.5</v>
+        <v>30.35</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>99517</v>
+        <v>3651</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>123426</v>
+        <v>4749</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>47.66</v>
+        <v>27.74</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -2511,31 +2511,31 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>3149.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>正達</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>105.25</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>103.75</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>4165</v>
+        <v>95906</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>5116</v>
+        <v>134795</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>75.51000000000001</v>
+        <v>101.44</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -2546,31 +2546,31 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>3362.TWO</t>
+          <t>6693.TWO</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>176.5</v>
+        <v>169</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>175.5</v>
+        <v>161</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>6954</v>
+        <v>1977</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>9400</v>
+        <v>2834</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0.7</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>133.52</v>
+        <v>152.55</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -2581,31 +2581,31 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>3653.TW</t>
+          <t>5701.TWO</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>劍湖山</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>3835</v>
+        <v>4.93</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>3820</v>
+        <v>4.5</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1450</v>
+        <v>869</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1936</v>
+        <v>1160</v>
       </c>
       <c r="G60" s="5" t="n">
         <v>0.7</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>3652.5</v>
+        <v>4.37</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -2616,31 +2616,31 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>1319.TW</t>
+          <t>2812.TW</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>105</v>
+        <v>19.5</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>103</v>
+        <v>19.3</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>5358</v>
+        <v>13150</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>8243</v>
+        <v>18058</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>0.7</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>91.40000000000001</v>
+        <v>19.01</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -2651,31 +2651,31 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>2885.TW</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>105.25</v>
+        <v>63.9</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>103.75</v>
+        <v>62.3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>100138</v>
+        <v>23090</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>135641</v>
+        <v>32042</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>0.7</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>101.44</v>
+        <v>59.59</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -2686,31 +2686,31 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>3443.TW</t>
+          <t>6505.TW</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>4815</v>
+        <v>52.8</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>4455</v>
+        <v>51.9</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>1251</v>
+        <v>5681</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>1906</v>
+        <v>8079</v>
       </c>
       <c r="G63" s="10" t="n">
         <v>0.7</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>4621.09</v>
+        <v>52.15</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -2721,31 +2721,31 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>3357.TWO</t>
+          <t>6026.TWO</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>臺慶科</t>
+          <t>福邦證</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>322</v>
+        <v>17.25</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>307.5</v>
+        <v>16.65</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>14140</v>
+        <v>4364</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>19905</v>
+        <v>5831</v>
       </c>
       <c r="G64" s="5" t="n">
         <v>0.7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>278.7</v>
+        <v>16.74</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -2756,31 +2756,31 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>6862.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>202</v>
+        <v>418</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>201</v>
+        <v>403</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>1786</v>
+        <v>4953</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>2525</v>
+        <v>7477</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0.7</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>192.45</v>
+        <v>414.4</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -2791,31 +2791,31 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>6155.TW</t>
+          <t>1612.TW</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>宏泰</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>90.2</v>
+        <v>37.7</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>89.5</v>
+        <v>37.3</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>18774</v>
+        <v>1126</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>31414</v>
+        <v>1759</v>
       </c>
       <c r="G66" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>69.63</v>
+        <v>37.39</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -2826,31 +2826,31 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>6409.TW</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>252</v>
+        <v>930</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>249.5</v>
+        <v>874</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>10452</v>
+        <v>1519</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>16364</v>
+        <v>2639</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0.6</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>230.38</v>
+        <v>768.85</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -2861,31 +2861,31 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>4919.TW</t>
+          <t>4763.TW</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>193</v>
+        <v>44.45</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>188</v>
+        <v>44.2</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>7848</v>
+        <v>4867</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>13726</v>
+        <v>8356</v>
       </c>
       <c r="G68" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>187.08</v>
+        <v>42.78</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -2896,31 +2896,31 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>3450.TW</t>
+          <t>2457.TW</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>飛宏</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>507</v>
+        <v>30.1</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>482</v>
+        <v>29.9</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>5448</v>
+        <v>9031</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>9659</v>
+        <v>15160</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>0.6</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>486.28</v>
+        <v>27.28</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -2931,31 +2931,31 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1809.TW</t>
+          <t>2030.TW</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>中釉</t>
+          <t>彰源</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>51.5</v>
+        <v>18.45</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>51.4</v>
+        <v>18.25</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6650</v>
+        <v>1317</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>14735</v>
+        <v>2363</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>48.27</v>
+        <v>17.63</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -2966,31 +2966,31 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>5876.TW</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>940</v>
+        <v>42.5</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>919</v>
+        <v>42</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>42057</v>
+        <v>8352</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>76484</v>
+        <v>15094</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>732.98</v>
+        <v>40.51</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3001,31 +3001,31 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>3023.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>319</v>
+        <v>15.6</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>317</v>
+        <v>14.25</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>974</v>
+        <v>21254</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1790</v>
+        <v>34326</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>314.42</v>
+        <v>15.22</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3036,31 +3036,31 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>6207.TWO</t>
+          <t>6209.TW</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>136</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>7618</v>
+        <v>13703</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>16765</v>
+        <v>24861</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>116.48</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3071,33 +3071,173 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>8996.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>1255</v>
+        <v>25.5</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>1225</v>
+        <v>25.45</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1445</v>
+        <v>7735</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>4072</v>
+        <v>14367</v>
       </c>
       <c r="G74" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>2427.TW</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>三商電</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>808</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>1840</v>
+      </c>
+      <c r="G75" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="H74" s="3" t="n">
-        <v>1139.2</v>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
+      <c r="H75" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>4939.TWO</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>亞電</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>12882</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>34025</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>8935.TWO</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>邦泰</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>432</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>1059</v>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>4542.TWO</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>科嶠</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>323</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>472</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>3097</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>272.77</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -3178,6 +3318,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
